--- a/artfynd/A 45121-2023 artfynd.xlsx
+++ b/artfynd/A 45121-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45121-2023 artfynd.xlsx
+++ b/artfynd/A 45121-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6915,6 +6915,363 @@
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127389794</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>102611</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Stenfalk</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Falco columbarius</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Södra Långträskheden, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>745074</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7261388</v>
+      </c>
+      <c r="S59" t="n">
+        <v>23</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kerstin Ulfendahl</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kerstin Ulfendahl, Per Johan Ulfendahl</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127389809</v>
+      </c>
+      <c r="B60" t="n">
+        <v>58334</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Södra Långträskheden, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>745074</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7261388</v>
+      </c>
+      <c r="S60" t="n">
+        <v>23</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kerstin Ulfendahl</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kerstin Ulfendahl, Per Johan Ulfendahl</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127389802</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58092</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Södra Långträskheden, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>745074</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7261388</v>
+      </c>
+      <c r="S61" t="n">
+        <v>23</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kerstin Ulfendahl</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kerstin Ulfendahl, Per Johan Ulfendahl</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45121-2023 artfynd.xlsx
+++ b/artfynd/A 45121-2023 artfynd.xlsx
@@ -6917,32 +6917,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127389794</v>
+        <v>127389809</v>
       </c>
       <c r="B59" t="n">
-        <v>57685</v>
+        <v>58334</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102611</v>
+        <v>103044</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6954,7 +6954,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7036,32 +7036,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127389809</v>
+        <v>127389794</v>
       </c>
       <c r="B60" t="n">
-        <v>58334</v>
+        <v>57685</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103044</v>
+        <v>102611</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7073,7 +7073,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 45121-2023 artfynd.xlsx
+++ b/artfynd/A 45121-2023 artfynd.xlsx
@@ -6917,32 +6917,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127389809</v>
+        <v>127389794</v>
       </c>
       <c r="B59" t="n">
-        <v>58334</v>
+        <v>57685</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103044</v>
+        <v>102611</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6954,7 +6954,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7036,32 +7036,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127389794</v>
+        <v>127389809</v>
       </c>
       <c r="B60" t="n">
-        <v>57685</v>
+        <v>58334</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102611</v>
+        <v>103044</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7073,7 +7073,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 45121-2023 artfynd.xlsx
+++ b/artfynd/A 45121-2023 artfynd.xlsx
@@ -6920,7 +6920,7 @@
         <v>127389809</v>
       </c>
       <c r="B59" t="n">
-        <v>58334</v>
+        <v>58338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kerstin Ulfendahl, Per Johan Ulfendahl</t>
+          <t>Per Johan Ulfendahl, Kerstin Ulfendahl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7039,7 +7039,7 @@
         <v>127389794</v>
       </c>
       <c r="B60" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kerstin Ulfendahl, Per Johan Ulfendahl</t>
+          <t>Per Johan Ulfendahl, Kerstin Ulfendahl</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7158,7 +7158,7 @@
         <v>127389802</v>
       </c>
       <c r="B61" t="n">
-        <v>58092</v>
+        <v>58096</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kerstin Ulfendahl, Per Johan Ulfendahl</t>
+          <t>Per Johan Ulfendahl, Kerstin Ulfendahl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 45121-2023 artfynd.xlsx
+++ b/artfynd/A 45121-2023 artfynd.xlsx
@@ -6917,32 +6917,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127389809</v>
+        <v>127389794</v>
       </c>
       <c r="B59" t="n">
-        <v>58338</v>
+        <v>57689</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103044</v>
+        <v>102611</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6954,7 +6954,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7029,39 +7029,39 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Per Johan Ulfendahl, Kerstin Ulfendahl</t>
+          <t>Kerstin Ulfendahl, Per Johan Ulfendahl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127389794</v>
+        <v>127389809</v>
       </c>
       <c r="B60" t="n">
-        <v>57689</v>
+        <v>58338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102611</v>
+        <v>103044</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7073,7 +7073,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Per Johan Ulfendahl, Kerstin Ulfendahl</t>
+          <t>Kerstin Ulfendahl, Per Johan Ulfendahl</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Per Johan Ulfendahl, Kerstin Ulfendahl</t>
+          <t>Kerstin Ulfendahl, Per Johan Ulfendahl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 45121-2023 artfynd.xlsx
+++ b/artfynd/A 45121-2023 artfynd.xlsx
@@ -6920,7 +6920,7 @@
         <v>127389794</v>
       </c>
       <c r="B59" t="n">
-        <v>57689</v>
+        <v>57691</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>127389809</v>
       </c>
       <c r="B60" t="n">
-        <v>58338</v>
+        <v>58340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>127389802</v>
       </c>
       <c r="B61" t="n">
-        <v>58096</v>
+        <v>58098</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 45121-2023 artfynd.xlsx
+++ b/artfynd/A 45121-2023 artfynd.xlsx
@@ -6920,7 +6920,7 @@
         <v>127389794</v>
       </c>
       <c r="B59" t="n">
-        <v>57691</v>
+        <v>57694</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>127389809</v>
       </c>
       <c r="B60" t="n">
-        <v>58340</v>
+        <v>58343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>127389802</v>
       </c>
       <c r="B61" t="n">
-        <v>58098</v>
+        <v>58101</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 45121-2023 artfynd.xlsx
+++ b/artfynd/A 45121-2023 artfynd.xlsx
@@ -6920,7 +6920,7 @@
         <v>127389794</v>
       </c>
       <c r="B59" t="n">
-        <v>57694</v>
+        <v>57700</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>127389809</v>
       </c>
       <c r="B60" t="n">
-        <v>58343</v>
+        <v>58349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>127389802</v>
       </c>
       <c r="B61" t="n">
-        <v>58101</v>
+        <v>58107</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 45121-2023 artfynd.xlsx
+++ b/artfynd/A 45121-2023 artfynd.xlsx
@@ -6917,32 +6917,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127389794</v>
+        <v>127389809</v>
       </c>
       <c r="B59" t="n">
-        <v>57700</v>
+        <v>58349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102611</v>
+        <v>103044</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6954,7 +6954,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7036,32 +7036,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127389809</v>
+        <v>127389794</v>
       </c>
       <c r="B60" t="n">
-        <v>58349</v>
+        <v>57700</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103044</v>
+        <v>102611</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7073,7 +7073,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
